--- a/Data/C07 Figures.xlsx
+++ b/Data/C07 Figures.xlsx
@@ -17827,7 +17827,7 @@
         <v>1008</v>
       </c>
       <c r="B411" t="n">
-        <v>2.0353770189504</v>
+        <v>2.0406570258012</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C07 Figures.xlsx
+++ b/Data/C07 Figures.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="1009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="1010">
   <si>
     <t xml:space="preserve">Ref_Date</t>
   </si>
@@ -3041,6 +3041,9 @@
   </si>
   <si>
     <t xml:space="preserve">Jul 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -17827,7 +17830,15 @@
         <v>1008</v>
       </c>
       <c r="B411" t="n">
-        <v>2.0406570258012</v>
+        <v>2.04153420818446</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B412" t="n">
+        <v>2.04923021348276</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C07 Figures.xlsx
+++ b/Data/C07 Figures.xlsx
@@ -17838,7 +17838,7 @@
         <v>1009</v>
       </c>
       <c r="B412" t="n">
-        <v>2.04923021348276</v>
+        <v>2.05432889632792</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C07 Figures.xlsx
+++ b/Data/C07 Figures.xlsx
@@ -3037,10 +3037,10 @@
     <t xml:space="preserve">Jun 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Jul 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jul 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Aug 2026</t>
@@ -14533,6 +14533,17 @@
         <v>2.71</v>
       </c>
     </row>
+    <row r="800">
+      <c r="A800" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B800" t="n">
+        <v>3.03214069132807</v>
+      </c>
+      <c r="C800" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -14550,7 +14561,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="2">
@@ -17827,7 +17838,7 @@
     </row>
     <row r="411">
       <c r="A411" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B411" t="n">
         <v>2.04153420818446</v>
@@ -17838,7 +17849,7 @@
         <v>1009</v>
       </c>
       <c r="B412" t="n">
-        <v>2.05432889632792</v>
+        <v>2.06309506034399</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C07 Figures.xlsx
+++ b/Data/C07 Figures.xlsx
@@ -3043,10 +3043,10 @@
     <t xml:space="preserve">Jul 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Aug 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aug 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Sep 2026</t>
@@ -5512,10 +5512,10 @@
         <v>186</v>
       </c>
       <c r="B185" t="n">
-        <v>1.67536809494672</v>
+        <v>1.6922082914486</v>
       </c>
       <c r="C185" t="n">
-        <v>0.908469462648783</v>
+        <v>0.908490282274562</v>
       </c>
     </row>
     <row r="186">
@@ -5523,10 +5523,10 @@
         <v>187</v>
       </c>
       <c r="B186" t="n">
-        <v>1.64208931201212</v>
+        <v>1.63857061537546</v>
       </c>
       <c r="C186" t="n">
-        <v>0.905913963486465</v>
+        <v>0.905871304477845</v>
       </c>
     </row>
     <row r="187">
@@ -5534,10 +5534,10 @@
         <v>188</v>
       </c>
       <c r="B187" t="n">
-        <v>1.6359694442512</v>
+        <v>1.62519181815396</v>
       </c>
       <c r="C187" t="n">
-        <v>0.913969089901001</v>
+        <v>0.914631766107545</v>
       </c>
     </row>
     <row r="188">
@@ -5545,10 +5545,10 @@
         <v>189</v>
       </c>
       <c r="B188" t="n">
-        <v>1.66939129703658</v>
+        <v>1.66733868314434</v>
       </c>
       <c r="C188" t="n">
-        <v>0.939930893218458</v>
+        <v>0.939363964151207</v>
       </c>
     </row>
     <row r="189">
@@ -5556,10 +5556,10 @@
         <v>190</v>
       </c>
       <c r="B189" t="n">
-        <v>1.70048481096372</v>
+        <v>1.71614157686127</v>
       </c>
       <c r="C189" t="n">
-        <v>0.968112820566438</v>
+        <v>0.967992046535988</v>
       </c>
     </row>
     <row r="190">
@@ -5567,10 +5567,10 @@
         <v>191</v>
       </c>
       <c r="B190" t="n">
-        <v>1.78851623442941</v>
+        <v>1.78619342451874</v>
       </c>
       <c r="C190" t="n">
-        <v>0.999013952423836</v>
+        <v>0.998888968413318</v>
       </c>
     </row>
     <row r="191">
@@ -5578,10 +5578,10 @@
         <v>192</v>
       </c>
       <c r="B191" t="n">
-        <v>1.81559344645855</v>
+        <v>1.80549595400434</v>
       </c>
       <c r="C191" t="n">
-        <v>0.986682457370167</v>
+        <v>0.987690926379082</v>
       </c>
     </row>
     <row r="192">
@@ -5589,10 +5589,10 @@
         <v>193</v>
       </c>
       <c r="B192" t="n">
-        <v>1.86601799450086</v>
+        <v>1.86319540047207</v>
       </c>
       <c r="C192" t="n">
-        <v>0.98193568308146</v>
+        <v>0.981242639503882</v>
       </c>
     </row>
     <row r="193">
@@ -5600,10 +5600,10 @@
         <v>194</v>
       </c>
       <c r="B193" t="n">
-        <v>1.9006755804301</v>
+        <v>1.91430955199996</v>
       </c>
       <c r="C193" t="n">
-        <v>0.975977895383307</v>
+        <v>0.975746066347906</v>
       </c>
     </row>
     <row r="194">
@@ -5611,10 +5611,10 @@
         <v>195</v>
       </c>
       <c r="B194" t="n">
-        <v>1.95207727438085</v>
+        <v>1.95159141934526</v>
       </c>
       <c r="C194" t="n">
-        <v>0.978951693665586</v>
+        <v>0.978806857383719</v>
       </c>
     </row>
     <row r="195">
@@ -5622,10 +5622,10 @@
         <v>196</v>
       </c>
       <c r="B195" t="n">
-        <v>1.98897866418721</v>
+        <v>1.98045747220905</v>
       </c>
       <c r="C195" t="n">
-        <v>0.987255576357749</v>
+        <v>0.988449539732508</v>
       </c>
     </row>
     <row r="196">
@@ -5633,10 +5633,10 @@
         <v>197</v>
       </c>
       <c r="B196" t="n">
-        <v>2.00773395616892</v>
+        <v>2.00386395442642</v>
       </c>
       <c r="C196" t="n">
-        <v>0.979243879303598</v>
+        <v>0.97836276593133</v>
       </c>
     </row>
     <row r="197">
@@ -5644,10 +5644,10 @@
         <v>198</v>
       </c>
       <c r="B197" t="n">
-        <v>2.01548946113031</v>
+        <v>2.02601839468342</v>
       </c>
       <c r="C197" t="n">
-        <v>0.978546880671824</v>
+        <v>0.978237392456351</v>
       </c>
     </row>
     <row r="198">
@@ -5655,10 +5655,10 @@
         <v>199</v>
       </c>
       <c r="B198" t="n">
-        <v>2.00308848394088</v>
+        <v>2.00467316710369</v>
       </c>
       <c r="C198" t="n">
-        <v>0.98004755386932</v>
+        <v>0.979915936422319</v>
       </c>
     </row>
     <row r="199">
@@ -5666,10 +5666,10 @@
         <v>200</v>
       </c>
       <c r="B199" t="n">
-        <v>2.00591988451422</v>
+        <v>2.00030400028612</v>
       </c>
       <c r="C199" t="n">
-        <v>0.978588167340797</v>
+        <v>0.979872689578649</v>
       </c>
     </row>
     <row r="200">
@@ -5677,10 +5677,10 @@
         <v>201</v>
       </c>
       <c r="B200" t="n">
-        <v>1.98868278775084</v>
+        <v>1.98247499235574</v>
       </c>
       <c r="C200" t="n">
-        <v>0.978336558251256</v>
+        <v>0.977658449048156</v>
       </c>
     </row>
     <row r="201">
@@ -5688,10 +5688,10 @@
         <v>202</v>
       </c>
       <c r="B201" t="n">
-        <v>1.95523440018676</v>
+        <v>1.96380503318938</v>
       </c>
       <c r="C201" t="n">
-        <v>0.976832956098968</v>
+        <v>0.976349059245139</v>
       </c>
     </row>
     <row r="202">
@@ -5699,10 +5699,10 @@
         <v>203</v>
       </c>
       <c r="B202" t="n">
-        <v>1.92520159223443</v>
+        <v>1.92792895197438</v>
       </c>
       <c r="C202" t="n">
-        <v>0.962142512799314</v>
+        <v>0.962064973723862</v>
       </c>
     </row>
     <row r="203">
@@ -5710,10 +5710,10 @@
         <v>204</v>
       </c>
       <c r="B203" t="n">
-        <v>1.91959459777676</v>
+        <v>1.91651822554013</v>
       </c>
       <c r="C203" t="n">
-        <v>0.968432082199543</v>
+        <v>0.969739939360324</v>
       </c>
     </row>
     <row r="204">
@@ -5721,10 +5721,10 @@
         <v>205</v>
       </c>
       <c r="B204" t="n">
-        <v>1.90052768326429</v>
+        <v>1.89234656781804</v>
       </c>
       <c r="C204" t="n">
-        <v>0.964938059310884</v>
+        <v>0.964175068440232</v>
       </c>
     </row>
     <row r="205">
@@ -5732,10 +5732,10 @@
         <v>206</v>
       </c>
       <c r="B205" t="n">
-        <v>1.89325472229353</v>
+        <v>1.90120416550445</v>
       </c>
       <c r="C205" t="n">
-        <v>0.971749659636212</v>
+        <v>0.971397524878411</v>
       </c>
     </row>
     <row r="206">
@@ -5743,10 +5743,10 @@
         <v>207</v>
       </c>
       <c r="B206" t="n">
-        <v>1.92385581509184</v>
+        <v>1.92550593923389</v>
       </c>
       <c r="C206" t="n">
-        <v>0.991526631205694</v>
+        <v>0.991728193953754</v>
       </c>
     </row>
   </sheetData>
@@ -14561,6 +14561,17 @@
         <v>2.82</v>
       </c>
     </row>
+    <row r="801">
+      <c r="A801" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B801" t="n">
+        <v>3.03398058252426</v>
+      </c>
+      <c r="C801" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -14578,7 +14589,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="2">
@@ -17863,7 +17874,7 @@
     </row>
     <row r="412">
       <c r="A412" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B412" t="n">
         <v>2.08020396681122</v>
@@ -17874,7 +17885,7 @@
         <v>1011</v>
       </c>
       <c r="B413" t="n">
-        <v>2.2536046481946</v>
+        <v>2.28075720292867</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C07 Figures.xlsx
+++ b/Data/C07 Figures.xlsx
@@ -17885,7 +17885,7 @@
         <v>1011</v>
       </c>
       <c r="B413" t="n">
-        <v>2.28075720292867</v>
+        <v>2.28054075816041</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C07 Figures.xlsx
+++ b/Data/C07 Figures.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="1012">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="1013">
   <si>
     <t xml:space="preserve">Ref_Date</t>
   </si>
@@ -3050,6 +3050,9 @@
   </si>
   <si>
     <t xml:space="preserve">Sep 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 2026</t>
   </si>
 </sst>
 </file>
@@ -17888,6 +17891,14 @@
         <v>2.28054075816041</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B414" t="n">
+        <v>2.26777743687243</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
